--- a/Papers/bibliography.xlsx
+++ b/Papers/bibliography.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PortableGit\MPhys-Superconductors\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE840D6-EAED-4D40-8C57-BE1F432DBC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC90F6BE-AD1E-4E41-B8A0-48A1B93E730B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3490C670-5B71-4312-99A0-2544537420CD}"/>
+    <workbookView xWindow="-11580" yWindow="4275" windowWidth="21600" windowHeight="11385" xr2:uid="{3490C670-5B71-4312-99A0-2544537420CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
   <si>
     <t>Ref #</t>
   </si>
@@ -181,6 +181,30 @@
   </si>
   <si>
     <t>Hidetoshi FUKUY AMA</t>
+  </si>
+  <si>
+    <t>Rashba_SemiConductor</t>
+  </si>
+  <si>
+    <t>Anomalous_Hall_Conductivity</t>
+  </si>
+  <si>
+    <t>G. A. H. Schober et al.</t>
+  </si>
+  <si>
+    <t>Mechanisms of enhanced orbital dia- and paramagnetism: Application to the Rashba semiconductor BiTeI</t>
+  </si>
+  <si>
+    <t>General susceptibility</t>
+  </si>
+  <si>
+    <t>Ab initio calculation of the anomalous Hall conductivity by Wannier interpolation</t>
+  </si>
+  <si>
+    <t>Xinjie Wang et al.</t>
+  </si>
+  <si>
+    <t>Maximally localized Wannier functions for entangled energy bands</t>
   </si>
 </sst>
 </file>
@@ -222,10 +246,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -276,17 +303,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8E54A4E3-7258-4FA5-9431-BDF1A45EC4BD}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8E54A4E3-7258-4FA5-9431-BDF1A45EC4BD}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="9" dataDxfId="0">
   <autoFilter ref="A1:H1048576" xr:uid="{8E54A4E3-7258-4FA5-9431-BDF1A45EC4BD}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{63F0DE14-C8A3-4F84-B63C-7FED8292FBCD}" name="Ref #" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{F5887866-BAEB-4604-BB6B-5716DCAD9D8A}" name="File Name" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{08FA91ED-27C9-4EAD-9FD1-43DC81347156}" name="Author" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{993674C3-E398-48F8-AC74-0547355664B4}" name="Title" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{C1A2B6C8-D9F9-47FD-AE17-1CA1EDE53F73}" name="Section Title" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{965C4D64-8B8C-4BBA-80C9-4F0B3C639248}" name="Type" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{1858D630-4E59-4E8C-A2EF-64C97512552C}" name="Key words" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E34A58B2-1983-4B6D-AC80-B8DD3D77C2F6}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{63F0DE14-C8A3-4F84-B63C-7FED8292FBCD}" name="Ref #" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{F5887866-BAEB-4604-BB6B-5716DCAD9D8A}" name="File Name" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{08FA91ED-27C9-4EAD-9FD1-43DC81347156}" name="Author" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{993674C3-E398-48F8-AC74-0547355664B4}" name="Title" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{C1A2B6C8-D9F9-47FD-AE17-1CA1EDE53F73}" name="Section Title" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{965C4D64-8B8C-4BBA-80C9-4F0B3C639248}" name="Type" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{1858D630-4E59-4E8C-A2EF-64C97512552C}" name="Key words" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E34A58B2-1983-4B6D-AC80-B8DD3D77C2F6}" name="Notes" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -589,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EC5F2AE-B8D5-4ED4-9204-72D1635BF073}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" customWidth="1"/>
@@ -830,10 +857,10 @@
       <c r="B11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="2" t="s">
         <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -841,6 +868,48 @@
       </c>
       <c r="G11" s="1" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
